--- a/public/sample/sample_record_file.xlsx
+++ b/public/sample/sample_record_file.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>Name</t>
   </si>
@@ -61,15 +61,9 @@
     <t>Amit Kapoor</t>
   </si>
   <si>
-    <t>9127150108</t>
-  </si>
-  <si>
     <t>9955186204</t>
   </si>
   <si>
-    <t>9232114136</t>
-  </si>
-  <si>
     <t>9892996651</t>
   </si>
   <si>
@@ -91,15 +85,9 @@
     <t>9905311545</t>
   </si>
   <si>
-    <t>vikas.mehra@yopmail.com</t>
-  </si>
-  <si>
     <t>vikas.singh@yopmail.com</t>
   </si>
   <si>
-    <t>rohan.verma@yopmail.com</t>
-  </si>
-  <si>
     <t>anjali.kapoor@yopmail.com</t>
   </si>
   <si>
@@ -124,9 +112,6 @@
     <t>Punjab Technical Campus</t>
   </si>
   <si>
-    <t>Global Institute</t>
-  </si>
-  <si>
     <t>City Group of Institutes</t>
   </si>
   <si>
@@ -149,13 +134,22 @@
   </si>
   <si>
     <t>B.Com</t>
+  </si>
+  <si>
+    <t>Government Polytechnic College, Ambota (Una)</t>
+  </si>
+  <si>
+    <t>rohan1.verma@yopmail.com</t>
+  </si>
+  <si>
+    <t>vikas1.mehra@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +164,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -204,16 +205,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -507,7 +514,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="48.44140625" customWidth="1"/>
+    <col min="4" max="4" width="47.5546875" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
@@ -533,17 +546,17 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
+      <c r="B2">
+        <v>9127150101</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -554,16 +567,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>8</v>
@@ -573,17 +586,17 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
+      <c r="B4">
+        <v>9232114132</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -594,16 +607,16 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -614,16 +627,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -634,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -654,16 +667,16 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -674,16 +687,16 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -694,16 +707,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -714,22 +727,26 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F11">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>